--- a/data/berita_2026-07-31.xlsx
+++ b/data/berita_2026-07-31.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -550,8 +550,350 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cara membuat SIM A baru 2026: Syarat, biaya, dan panduan daftar online lengkap</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 08:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Surat Izin Mengemudi (SIM) A merupakan dokumen wajib yang harus dimiliki setiap pengendara mobil di Indonesia. Selain ...</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5673700/cara-membuat-sim-a-baru-2026-syarat-biaya-dan-panduan-daftar-online-lengkap</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/1000623631.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cara membuat SIM C baru 2026: Syarat, biaya, dan panduan daftar online</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 06:36:55 +0700</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Surat Izin Mengemudi (SIM) C merupakan dokumen wajib yang harus dimiliki setiap pengendara sepeda motor di Indonesia. ...</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5673645/cara-membuat-sim-c-baru-2026-syarat-biaya-dan-panduan-daftar-online</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/pelayanan-perpanjangan-sim-keliling-selama-24-jam-2830529.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cara perpanjang SIM online 2026: syarat, biaya, dan panduan lengkap lewat Digital Korlantas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 06:28:28 +0700</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Perpanjangan Surat Izin Mengemudi (SIM) kini semakin praktis karena dapat dilakukan secara online tanpa harus datang ...</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5673636/cara-perpanjang-sim-online-2026-syarat-biaya-dan-panduan-lengkap-lewat-digital-korlantas</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/02/06/SIM.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sepakbola</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Daftar pemain Indonesia All Stars vs Aston Villa, Ezra Walian jadi kapten</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 13:34:51 +0700</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Indonesia All Stars telah menyiapkan skuad untuk menghadapi klub Liga Inggris Aston Villa dalam laga pramusim di ...</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5674073/daftar-pemain-indonesia-all-stars-vs-aston-villa-ezra-walian-jadi-kapten</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/tim-sepak-bola-aston-villa-tiba-di-indonesia-2831035.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Humaniora</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jadwal puasa sunnah Agustus 2026 lengkap: Senin Kamis, Ayyamul Bidh, Daud, dan niat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 06:18:47 +0700</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Umat Islam dapat menunaikan sejumlah puasa sunnah pada Agustus 2026, mulai dari puasa Senin Kamis hingga Ayyamul Bidh ...</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://ramadhan.antaranews.com/berita/5673632/jadwal-puasa-sunnah-agustus-2026-lengkap-senin-kamis-ayyamul-bidh-daud-dan-niat</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/21/232332.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Hiburan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10 film dan serial Netflix terbaru tayang Agustus 2026, ada Dilan ITB 1997 hingga Outer Banks 5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 07:58:37 +0700</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Netflix kembali menghadirkan berbagai film dan serial terbaru yang siap menemani penonton sepanjang Agustus 2026. ...</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5673691/10-film-dan-serial-netflix-terbaru-tayang-agustus-2026-ada-dilan-itb-1997-hingga-outer-banks-5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/30/image0-14.jpeg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tekno</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sisa kuota bisa dibawa? Ini cara aktifkan kuota rollover di Telkomsel, Indosat, dan XL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 08:30:49 +0700</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fitur kuota internet rollover atau akumulasi kuota menjadi perhatian pengguna layanan seluler setelah adanya putusan ...</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5673721/sisa-kuota-bisa-dibawa-ini-cara-aktifkan-kuota-rollover-di-telkomsel-indosat-dan-xl</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/23/1000001944.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tekno</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5 HP murah 128GB di bawah Rp2 juta terbaik 2026, RAM besar dan baterai awet</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 06:42:51 +0700</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pasar ponsel pintar kelas entry-level pada 2026 semakin menawarkan pilihan menarik dengan penyimpanan 128GB dan harga ...</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5673649/5-hp-murah-128gb-di-bawah-rp2-juta-terbaik-2026-ram-besar-dan-baterai-awet</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/01/16/InShot_20250116_111246588.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tekno</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nomor HP hilang? Begini cara blokir kartu SIM agar tidak disalahgunakan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 06:32:54 +0700</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kehilangan ponsel atau kartu SIM perlu segera ditangani agar nomor telepon tidak disalahgunakan untuk penipuan, ...</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5673641/nomor-hp-hilang-begini-cara-blokir-kartu-sim-agar-tidak-disalahgunakan</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/10/IMG-20260610-WA0006-1.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-07-31.xlsx
+++ b/data/berita_2026-07-31.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -430,6 +430,7 @@
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,6 +474,11 @@
           <t>Media</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Sentimen</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,6 +517,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -549,6 +556,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -587,6 +595,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,6 +634,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -663,6 +673,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -701,6 +712,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -739,6 +751,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -777,6 +790,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -815,6 +829,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -853,6 +868,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -891,9 +907,10 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
+  <autoFilter ref="A1:I12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>